--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.26947640178503</v>
+        <v>6.706289915290067</v>
       </c>
       <c r="D2" t="n">
-        <v>42.78192957570282</v>
+        <v>6.952063556051709</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2754532057636</v>
+        <v>1.832261145936584</v>
       </c>
       <c r="F2" t="n">
-        <v>13.07212966829353</v>
+        <v>2.124221071097698</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.831375284735259</v>
+        <v>1.11009848376948</v>
       </c>
       <c r="D3" t="n">
-        <v>5.930255390291624</v>
+        <v>0.9636665009223889</v>
       </c>
       <c r="E3" t="n">
-        <v>11.2754532057636</v>
+        <v>1.832261145936584</v>
       </c>
       <c r="F3" t="n">
-        <v>13.07212966829353</v>
+        <v>2.124221071097698</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.37446004473819</v>
+        <v>3.473349757269956</v>
       </c>
       <c r="D4" t="n">
-        <v>6.758185423194515</v>
+        <v>1.098205131269109</v>
       </c>
       <c r="E4" t="n">
-        <v>11.2754532057636</v>
+        <v>1.832261145936584</v>
       </c>
       <c r="F4" t="n">
-        <v>13.07212966829353</v>
+        <v>2.124221071097698</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.45383567078651</v>
+        <v>3.648748296502809</v>
       </c>
       <c r="D5" t="n">
-        <v>23.84060184781233</v>
+        <v>3.874097800269504</v>
       </c>
       <c r="E5" t="n">
-        <v>11.2754532057636</v>
+        <v>1.832261145936584</v>
       </c>
       <c r="F5" t="n">
-        <v>13.07212966829353</v>
+        <v>2.124221071097698</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.07700521144725</v>
+        <v>1.637513346860178</v>
       </c>
       <c r="D6" t="n">
-        <v>8.921042654665577</v>
+        <v>1.449669431383156</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2754532057636</v>
+        <v>1.832261145936584</v>
       </c>
       <c r="F6" t="n">
-        <v>13.07212966829353</v>
+        <v>2.124221071097698</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.18066348001104</v>
+        <v>5.554357815501795</v>
       </c>
       <c r="D7" t="n">
-        <v>32.66740975327998</v>
+        <v>5.308454084907997</v>
       </c>
       <c r="E7" t="n">
-        <v>11.2754532057636</v>
+        <v>1.832261145936584</v>
       </c>
       <c r="F7" t="n">
-        <v>13.07212966829353</v>
+        <v>2.124221071097698</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.33585796505881</v>
+        <v>3.792076919322056</v>
       </c>
       <c r="D8" t="n">
-        <v>22.80058422106411</v>
+        <v>3.705094935922917</v>
       </c>
       <c r="E8" t="n">
-        <v>11.2754532057636</v>
+        <v>1.832261145936584</v>
       </c>
       <c r="F8" t="n">
-        <v>13.07212966829353</v>
+        <v>2.124221071097698</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
